--- a/artfynd/A 42628-2025 artfynd.xlsx
+++ b/artfynd/A 42628-2025 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>127935625</v>
       </c>
       <c r="B4" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42628-2025 artfynd.xlsx
+++ b/artfynd/A 42628-2025 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>127935625</v>
       </c>
       <c r="B4" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42628-2025 artfynd.xlsx
+++ b/artfynd/A 42628-2025 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>127935625</v>
       </c>
       <c r="B4" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42628-2025 artfynd.xlsx
+++ b/artfynd/A 42628-2025 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>127935625</v>
       </c>
       <c r="B4" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42628-2025 artfynd.xlsx
+++ b/artfynd/A 42628-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,73 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79651925</v>
+        <v>96456353</v>
       </c>
       <c r="B2" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221849</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsboda, Vstm</t>
+          <t>Sundsboda, Grönbo, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522752.4709776017</v>
+        <v>522942</v>
       </c>
       <c r="R2" t="n">
-        <v>6609293.963907463</v>
+        <v>6609236</v>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,76 +763,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant vid skogsbryn av grov flerskiktad sandtallskog på rullstensås.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Grus (2-60 mm)</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Gravel (2-60 mm)</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96456353</v>
+        <v>79651816</v>
       </c>
       <c r="B3" t="n">
-        <v>87997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1596</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -868,19 +821,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsboda, Grönbo, Vstm</t>
+          <t>Sundsboda, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522942.3624373913</v>
+        <v>522853</v>
       </c>
       <c r="R3" t="n">
-        <v>6609236.435023213</v>
+        <v>6609303</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -907,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,33 +876,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>grov flerskiktad barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127935625</v>
+        <v>127935549</v>
       </c>
       <c r="B4" t="n">
-        <v>91484</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522914</v>
+        <v>522993</v>
       </c>
       <c r="R4" t="n">
-        <v>6609154</v>
+        <v>6609447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +989,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,6 +1004,969 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127935625</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522914</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6609154</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96466927</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallfallsmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522808</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6609306</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127935767</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522996</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6609452</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127935507</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522971</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6609327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127935569</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>522994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6609451</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127935769</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>522980</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6609361</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127935719</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>522858</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6609313</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Ellen Hultman</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>79651925</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundsboda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>522752</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6609294</v>
+      </c>
+      <c r="S12" t="n">
+        <v>32</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-08-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Vägkant vid skogsbryn av grov flerskiktad sandtallskog på rullstensås.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Grus (2-60 mm)</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Gravel (2-60 mm)</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127935766</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Morskoga NVI, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>522978</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6609362</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42628-2025 artfynd.xlsx
+++ b/artfynd/A 42628-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96456353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935625</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79651816</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935549</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96466927</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935507</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935569</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935769</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935719</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79651925</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,8 +2027,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127935766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>